--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>STATUS</t>
+  </si>
   <si>
     <t>URL</t>
   </si>
@@ -35,13 +38,40 @@
     <t>PASSWORD</t>
   </si>
   <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>MERCHANTID</t>
+  </si>
+  <si>
     <t>https://seel-test-alexsong-1214.myshopify.com/</t>
   </si>
   <si>
     <t>seel</t>
   </si>
   <si>
+    <t>seel-test-alexsong-1214.myshopify.com</t>
+  </si>
+  <si>
+    <t>20260424202579829682</t>
+  </si>
+  <si>
     <t>https://www.gravastar.com/</t>
+  </si>
+  <si>
+    <t>gravastar-com.myshopify.com</t>
+  </si>
+  <si>
+    <t>20250320202423842967</t>
+  </si>
+  <si>
+    <t>https://www.djiusa.com/</t>
+  </si>
+  <si>
+    <t>prqjdj-v9.myshopify.com</t>
+  </si>
+  <si>
+    <t>20260402203053590116</t>
   </si>
 </sst>
 </file>
@@ -657,9 +687,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1186,36 +1225,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="47.6153846153846" customWidth="1"/>
-    <col min="2" max="2" width="37.4903846153846" customWidth="1"/>
-    <col min="3" max="16382" width="19.0673076923077" customWidth="1"/>
+    <col min="1" max="1" width="19.0673076923077" style="1"/>
+    <col min="2" max="2" width="47.6153846153846" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.4615384615385" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.4615384615385" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.1538461538462" style="1" customWidth="1"/>
+    <col min="6" max="16383" width="19.0673076923077" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="19.0673076923077" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>4</v>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B4" r:id="rId1" display="https://www.djiusa.com/"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>STATUS</t>
   </si>
@@ -44,6 +44,9 @@
     <t>MERCHANTID</t>
   </si>
   <si>
+    <t>MODE</t>
+  </si>
+  <si>
     <t>https://seel-test-alexsong-1214.myshopify.com/</t>
   </si>
   <si>
@@ -72,6 +75,15 @@
   </si>
   <si>
     <t>20260402203053590116</t>
+  </si>
+  <si>
+    <t>https://seel-test-ew01.myshopify.com/</t>
+  </si>
+  <si>
+    <t>seel-test-ew01.myshopify.com</t>
+  </si>
+  <si>
+    <t>20250429201112929308</t>
   </si>
 </sst>
 </file>
@@ -1225,8 +1237,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="19.0673076923077" style="1"/>
     <col min="2" max="2" width="47.6153846153846" style="1" customWidth="1"/>
@@ -1237,7 +1249,7 @@
     <col min="16384" max="16384" width="19.0673076923077" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1253,55 +1265,76 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" display="https://www.djiusa.com/"/>
+    <hyperlink ref="B5" r:id="rId2" display="https://seel-test-ew01.myshopify.com/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -1,257 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13500"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29100" windowHeight="13500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>PASSWORD</t>
-  </si>
-  <si>
-    <t>DOMAIN</t>
-  </si>
-  <si>
-    <t>MERCHANTID</t>
-  </si>
-  <si>
-    <t>MODE</t>
-  </si>
-  <si>
-    <t>https://seel-test-alexsong-1214.myshopify.com/</t>
-  </si>
-  <si>
-    <t>seel</t>
-  </si>
-  <si>
-    <t>seel-test-alexsong-1214.myshopify.com</t>
-  </si>
-  <si>
-    <t>20260424202579829682</t>
-  </si>
-  <si>
-    <t>https://www.gravastar.com/</t>
-  </si>
-  <si>
-    <t>gravastar-com.myshopify.com</t>
-  </si>
-  <si>
-    <t>20250320202423842967</t>
-  </si>
-  <si>
-    <t>https://www.djiusa.com/</t>
-  </si>
-  <si>
-    <t>prqjdj-v9.myshopify.com</t>
-  </si>
-  <si>
-    <t>20260402203053590116</t>
-  </si>
-  <si>
-    <t>https://seel-test-ew01.myshopify.com/</t>
-  </si>
-  <si>
-    <t>seel-test-ew01.myshopify.com</t>
-  </si>
-  <si>
-    <t>20250429201112929308</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -551,165 +471,165 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -957,7 +877,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -966,7 +886,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -979,11 +899,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1235,108 +1218,170 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="19.0673076923077" style="1"/>
-    <col min="2" max="2" width="47.6153846153846" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.4615384615385" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.4615384615385" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.1538461538462" style="1" customWidth="1"/>
-    <col min="6" max="16383" width="19.0673076923077" style="1" customWidth="1"/>
-    <col min="16384" max="16384" width="19.0673076923077" style="1"/>
+    <col width="19.0673076923077" customWidth="1" style="1" min="1" max="1"/>
+    <col width="47.6153846153846" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13.4615384615385" customWidth="1" style="1" min="3" max="3"/>
+    <col width="38.4615384615385" customWidth="1" style="1" min="4" max="4"/>
+    <col width="23.1538461538462" customWidth="1" style="1" min="5" max="5"/>
+    <col width="19.0673076923077" customWidth="1" style="1" min="6" max="16383"/>
+    <col width="19.0673076923077" customWidth="1" style="1" min="16384" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PASSWORD</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MERCHANTID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>https://seel-test-alexsong-1214.myshopify.com/</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>seel</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>seel-test-alexsong-1214.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>20260424202579829682</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>https://www.gravastar.com/</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>gravastar-com.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>20250320202423842967</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1">
+    <row r="4">
+      <c r="A4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.djiusa.com/</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>prqjdj-v9.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>20260402203053590116</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1">
+    <row r="5">
+      <c r="A5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1">
-        <v>0</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>18</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://seel-test-ew01.myshopify.com/</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>seel</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>seel-test-ew01.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>20250429201112929308</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" display="https://www.djiusa.com/"/>
-    <hyperlink ref="B5" r:id="rId2" display="https://seel-test-ew01.myshopify.com/"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" display="https://www.djiusa.com/" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="https://seel-test-ew01.myshopify.com/" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -1,177 +1,263 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29100" windowHeight="13500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="29100" windowHeight="13460"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>PASSWORD</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>MERCHANTID</t>
+  </si>
+  <si>
+    <t>MODE</t>
+  </si>
+  <si>
+    <t>https://seel-test-alexsong-1214.myshopify.com/</t>
+  </si>
+  <si>
+    <t>seel</t>
+  </si>
+  <si>
+    <t>seel-test-alexsong-1214.myshopify.com</t>
+  </si>
+  <si>
+    <t>20260424202579829682</t>
+  </si>
+  <si>
+    <t>OFF</t>
+  </si>
+  <si>
+    <t>https://www.gravastar.com/</t>
+  </si>
+  <si>
+    <t>gravastar-com.myshopify.com</t>
+  </si>
+  <si>
+    <t>20250320202423842967</t>
+  </si>
+  <si>
+    <t>PRODUCTION</t>
+  </si>
+  <si>
+    <t>https://www.djiusa.com/</t>
+  </si>
+  <si>
+    <t>prqjdj-v9.myshopify.com</t>
+  </si>
+  <si>
+    <t>20260402203053590116</t>
+  </si>
+  <si>
+    <t>https://seel-test-ew01.myshopify.com/</t>
+  </si>
+  <si>
+    <t>seel-test-ew01.myshopify.com</t>
+  </si>
+  <si>
+    <t>20250429201112929308</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -471,165 +557,165 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -877,7 +963,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -886,7 +972,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -899,74 +985,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1218,170 +1241,119 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col width="19.0673076923077" customWidth="1" style="1" min="1" max="1"/>
-    <col width="47.6153846153846" customWidth="1" style="1" min="2" max="2"/>
-    <col width="13.4615384615385" customWidth="1" style="1" min="3" max="3"/>
-    <col width="38.4615384615385" customWidth="1" style="1" min="4" max="4"/>
-    <col width="23.1538461538462" customWidth="1" style="1" min="5" max="5"/>
-    <col width="19.0673076923077" customWidth="1" style="1" min="6" max="16383"/>
-    <col width="19.0673076923077" customWidth="1" style="1" min="16384" max="16384"/>
+    <col min="1" max="1" width="19.0673076923077" style="1" customWidth="1"/>
+    <col min="2" max="2" width="47.6153846153846" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.4615384615385" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.4615384615385" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.1538461538462" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="19.0673076923077" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>STATUS</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>PASSWORD</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>DOMAIN</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MERCHANTID</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>MODE</t>
-        </is>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>https://seel-test-alexsong-1214.myshopify.com/</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>seel</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>seel-test-alexsong-1214.myshopify.com</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>20260424202579829682</t>
-        </is>
-      </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>https://www.gravastar.com/</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>gravastar-com.myshopify.com</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>20250320202423842967</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.djiusa.com/</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>prqjdj-v9.myshopify.com</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>20260402203053590116</t>
-        </is>
-      </c>
-      <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
         <v>0</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>https://seel-test-ew01.myshopify.com/</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>seel</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>seel-test-ew01.myshopify.com</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>20250429201112929308</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1">
+        <v>123</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" display="https://www.djiusa.com/" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="https://seel-test-ew01.myshopify.com/" r:id="rId2"/>
+    <hyperlink ref="B4" r:id="rId1" display="https://www.djiusa.com/"/>
+    <hyperlink ref="B5" r:id="rId2" display="https://seel-test-ew01.myshopify.com/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>STATUS</t>
   </si>
@@ -1335,8 +1335,8 @@
       <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="1">
-        <v>123</v>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>19</v>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -1,263 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13460"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29100" windowHeight="13500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>PASSWORD</t>
-  </si>
-  <si>
-    <t>DOMAIN</t>
-  </si>
-  <si>
-    <t>MERCHANTID</t>
-  </si>
-  <si>
-    <t>MODE</t>
-  </si>
-  <si>
-    <t>https://seel-test-alexsong-1214.myshopify.com/</t>
-  </si>
-  <si>
-    <t>seel</t>
-  </si>
-  <si>
-    <t>seel-test-alexsong-1214.myshopify.com</t>
-  </si>
-  <si>
-    <t>20260424202579829682</t>
-  </si>
-  <si>
-    <t>OFF</t>
-  </si>
-  <si>
-    <t>https://www.gravastar.com/</t>
-  </si>
-  <si>
-    <t>gravastar-com.myshopify.com</t>
-  </si>
-  <si>
-    <t>20250320202423842967</t>
-  </si>
-  <si>
-    <t>PRODUCTION</t>
-  </si>
-  <si>
-    <t>https://www.djiusa.com/</t>
-  </si>
-  <si>
-    <t>prqjdj-v9.myshopify.com</t>
-  </si>
-  <si>
-    <t>20260402203053590116</t>
-  </si>
-  <si>
-    <t>https://seel-test-ew01.myshopify.com/</t>
-  </si>
-  <si>
-    <t>seel-test-ew01.myshopify.com</t>
-  </si>
-  <si>
-    <t>20250429201112929308</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -557,165 +471,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -963,7 +874,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -972,7 +883,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -985,11 +896,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1241,119 +1215,580 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="19.0673076923077" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="19.0673076923077" style="1" customWidth="1"/>
-    <col min="2" max="2" width="47.6153846153846" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.4615384615385" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.4615384615385" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.1538461538462" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="19.0673076923077" style="1" customWidth="1"/>
+    <col width="19.0673076923077" customWidth="1" style="1" min="1" max="1"/>
+    <col width="47.6153846153846" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13.4615384615385" customWidth="1" style="1" min="3" max="3"/>
+    <col width="38.4615384615385" customWidth="1" style="1" min="4" max="4"/>
+    <col width="23.1538461538462" customWidth="1" style="1" min="5" max="5"/>
+    <col width="19.0673076923077" customWidth="1" style="1" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PASSWORD</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MERCHANTID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1">
-        <v>0</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>https://www.gravastar.com/</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>gravastar-com.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>20250320202423842967</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>https://www.djiusa.com/</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>prqjdj-v9.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>20260402203053590116</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>https://klaiyi.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>klaiyi.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20250318202971766250</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>https://gravastar-com.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>gravastar-com.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20250320202423842967</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>https://18c8df-2.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>18c8df-2.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20250508202225129668</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>https://ezarc-tools.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>ezarc-tools.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20250613202550345763</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>https://unihertz-shop.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>unihertz-shop.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20250709202226700491</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>https://bigtree3d.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>bigtree3d.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20250710203877209377</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>https://tcl-rayneo.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>tcl-rayneo.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20250717202242559533</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>https://luffy-crystal.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>luffy-crystal.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20250811203028022026</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>https://fitueyes.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>fitueyes.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20250813202621494876</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>https://bfwguz-kr.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>bfwguz-kr.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20250927203010234649</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>https://maikr-9237.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>maikr-9237.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20260211200680384083</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>https://prqjdj-v9.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>prqjdj-v9.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>20260402203053590116</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>https://marketing-212684499424.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>marketing-212684499424.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20260427202837963063</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>https://elle-vane.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>elle-vane.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20260427203268924640</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>https://anorahair.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>anorahair.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20260427203321029964</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>https://gravastarde.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>gravastarde.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>20260428202439034135</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>https://gaslandus.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>gaslandus.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20260508203079512968</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>https://lubluelu.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>lubluelu.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>20260525202540306719</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>https://unm9zb-1q.myshopify.com</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>unm9zb-1q.myshopify.com</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20260527201323453882</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" display="https://www.djiusa.com/"/>
-    <hyperlink ref="B5" r:id="rId2" display="https://seel-test-ew01.myshopify.com/"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13500"/>
+    <workbookView windowWidth="29100" windowHeight="13480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="67">
   <si>
     <t>STATUS</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>MODE</t>
+  </si>
+  <si>
+    <t>THEMEINSTALLED</t>
   </si>
   <si>
     <t>https://www.gravastar.com/</t>
@@ -840,11 +843,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -1375,18 +1381,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="19.0673076923077" style="1" customWidth="1"/>
     <col min="2" max="2" width="47.6153846153846" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.4615384615385" style="1" customWidth="1"/>
     <col min="4" max="4" width="38.4615384615385" style="1" customWidth="1"/>
     <col min="5" max="5" width="23.1538461538462" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="19.0673076923077" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.0673076923077" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.3076923076923" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="19.0673076923077" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1405,365 +1413,434 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>0</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1">
-        <v>0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1">
-        <v>0</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1">
-        <v>0</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="1">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="E16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="E17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="E18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="E19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="E20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="E21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F22" t="s">
-        <v>9</v>
+      <c r="E22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B11" r:id="rId1" display="https://luffy-crystal.myshopify.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="68">
+  <si>
+    <t>ID</t>
+  </si>
   <si>
     <t>STATUS</t>
   </si>
@@ -843,7 +846,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -852,6 +855,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1381,20 +1387,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="19.0673076923077" style="1" customWidth="1"/>
-    <col min="2" max="2" width="47.6153846153846" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.4615384615385" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.4615384615385" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.1538461538462" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.0673076923077" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.3076923076923" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="19.0673076923077" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.0673076923077" style="1"/>
+    <col min="2" max="2" width="19.0673076923077" style="1" customWidth="1"/>
+    <col min="3" max="3" width="47.6153846153846" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.4615384615385" style="1" customWidth="1"/>
+    <col min="5" max="5" width="38.4615384615385" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.1538461538462" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.0673076923077" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.3076923076923" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="19.0673076923077" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1416,430 +1423,498 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1">
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1">
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1">
+      <c r="B17" s="1">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1">
+      <c r="B18" s="1">
         <v>0</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1" t="b">
+      <c r="B22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1">
-        <v>0</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1">
-        <v>0</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="1">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="1">
-        <v>0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1">
-        <v>0</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="1">
-        <v>0</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="1">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="1">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="1" t="b">
+      <c r="F22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="1" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B11" r:id="rId1" display="https://luffy-crystal.myshopify.com"/>
+    <hyperlink ref="C11" r:id="rId1" display="https://luffy-crystal.myshopify.com"/>
+    <hyperlink ref="C14" r:id="rId2" display="https://maikr-9237.myshopify.com"/>
+    <hyperlink ref="C15" r:id="rId3" display="https://prqjdj-v9.myshopify.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
@@ -1455,7 +1455,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>12</v>
@@ -1478,7 +1478,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>15</v>
@@ -1501,7 +1501,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -1524,7 +1524,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
@@ -1547,7 +1547,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>22</v>
@@ -1570,7 +1570,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>25</v>
@@ -1593,7 +1593,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -1616,7 +1616,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>31</v>
@@ -1639,7 +1639,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>34</v>
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>37</v>
@@ -1685,7 +1685,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>40</v>
@@ -1708,7 +1708,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>43</v>
@@ -1731,7 +1731,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>46</v>
@@ -1823,7 +1823,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>56</v>
@@ -1846,7 +1846,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>59</v>
@@ -1869,7 +1869,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>62</v>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$F$1:$F$20</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
   <si>
     <t>ID</t>
   </si>
@@ -83,9 +86,6 @@
     <t>20250318202971766250</t>
   </si>
   <si>
-    <t>https://gravastar-com.myshopify.com</t>
-  </si>
-  <si>
     <t>https://18c8df-2.myshopify.com</t>
   </si>
   <si>
@@ -165,9 +165,6 @@
   </si>
   <si>
     <t>20260211200680384083</t>
-  </si>
-  <si>
-    <t>https://prqjdj-v9.myshopify.com</t>
   </si>
   <si>
     <t>https://marketing-212684499424.myshopify.com</t>
@@ -854,10 +851,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1387,11 +1384,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="19.0673076923077" style="1"/>
-    <col min="2" max="2" width="19.0673076923077" style="1" customWidth="1"/>
+    <col min="1" max="2" width="19.0673076923077" style="1" customWidth="1"/>
     <col min="3" max="3" width="47.6153846153846" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.4615384615385" style="1" customWidth="1"/>
     <col min="5" max="5" width="38.4615384615385" style="1" customWidth="1"/>
@@ -1434,7 +1430,7 @@
       <c r="B2" s="1">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1457,7 +1453,7 @@
       <c r="B3" s="1">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1507,10 +1503,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>11</v>
@@ -1524,22 +1520,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1550,19 +1546,19 @@
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1573,13 +1569,13 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>11</v>
@@ -1596,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>11</v>
@@ -1616,22 +1612,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H10" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1641,20 +1637,20 @@
       <c r="B11" s="1">
         <v>0</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>34</v>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H11" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1665,13 +1661,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>11</v>
@@ -1687,14 +1683,14 @@
       <c r="B13" s="1">
         <v>0</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>40</v>
+      <c r="C13" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>11</v>
@@ -1710,14 +1706,14 @@
       <c r="B14" s="1">
         <v>0</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
+      <c r="C14" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>11</v>
@@ -1733,14 +1729,14 @@
       <c r="B15" s="1">
         <v>0</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>46</v>
+      <c r="C15" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>11</v>
@@ -1757,13 +1753,13 @@
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>11</v>
@@ -1780,13 +1776,13 @@
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>11</v>
@@ -1803,13 +1799,13 @@
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>11</v>
@@ -1826,13 +1822,13 @@
         <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>11</v>
@@ -1849,13 +1845,13 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>11</v>
@@ -1864,57 +1860,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="F1:F20" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="C11" r:id="rId1" display="https://luffy-crystal.myshopify.com"/>
-    <hyperlink ref="C14" r:id="rId2" display="https://maikr-9237.myshopify.com"/>
-    <hyperlink ref="C15" r:id="rId3" display="https://prqjdj-v9.myshopify.com"/>
+    <hyperlink ref="C2" r:id="rId1" display="https://www.gravastar.com/"/>
+    <hyperlink ref="C3" r:id="rId2" display="https://www.djiusa.com/" tooltip="https://www.djiusa.com/"/>
+    <hyperlink ref="C10" r:id="rId3" display="https://luffy-crystal.myshopify.com"/>
+    <hyperlink ref="C13" r:id="rId4" display="https://maikr-9237.myshopify.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -1428,7 +1428,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
@@ -1474,7 +1474,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>15</v>
@@ -1497,7 +1497,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -1543,7 +1543,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>24</v>
@@ -1566,7 +1566,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>27</v>
@@ -1635,7 +1635,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>36</v>
@@ -1658,7 +1658,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>39</v>
@@ -1681,7 +1681,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>42</v>
@@ -1704,7 +1704,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>45</v>
@@ -1727,7 +1727,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>48</v>
@@ -1750,7 +1750,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>51</v>
@@ -1773,7 +1773,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>54</v>
@@ -1796,7 +1796,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>57</v>
@@ -1819,7 +1819,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>60</v>
@@ -1842,7 +1842,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>63</v>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -122,7 +122,7 @@
     <t>20250710203877209377</t>
   </si>
   <si>
-    <t>https://tcl-rayneo.myshopify.com</t>
+    <t>https://www.rayneo.com/</t>
   </si>
   <si>
     <t>tcl-rayneo.myshopify.com</t>
@@ -843,7 +843,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -851,6 +851,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
@@ -1436,7 +1439,7 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1459,7 +1462,7 @@
       <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1482,7 +1485,7 @@
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -1505,7 +1508,7 @@
       <c r="E5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1528,7 +1531,7 @@
       <c r="E6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1551,7 +1554,7 @@
       <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1574,7 +1577,7 @@
       <c r="E8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1591,13 +1594,13 @@
       <c r="B9" s="1">
         <v>0</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>32</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -1614,13 +1617,13 @@
       <c r="B10" s="1">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -1643,7 +1646,7 @@
       <c r="E11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -1666,7 +1669,7 @@
       <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -1689,7 +1692,7 @@
       <c r="E13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>44</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -1712,7 +1715,7 @@
       <c r="E14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>47</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -1735,7 +1738,7 @@
       <c r="E15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="5" t="s">
         <v>50</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -1758,7 +1761,7 @@
       <c r="E16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1781,7 +1784,7 @@
       <c r="E17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -1804,7 +1807,7 @@
       <c r="E18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>59</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -1827,7 +1830,7 @@
       <c r="E19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>62</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -1850,7 +1853,7 @@
       <c r="E20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>65</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -1869,6 +1872,7 @@
     <hyperlink ref="C3" r:id="rId2" display="https://www.djiusa.com/" tooltip="https://www.djiusa.com/"/>
     <hyperlink ref="C10" r:id="rId3" display="https://luffy-crystal.myshopify.com"/>
     <hyperlink ref="C13" r:id="rId4" display="https://maikr-9237.myshopify.com"/>
+    <hyperlink ref="C9" r:id="rId5" display="https://www.rayneo.com/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -251,7 +251,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -259,7 +259,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -713,12 +713,12 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
@@ -843,21 +843,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1439,7 +1442,7 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1462,7 +1465,7 @@
       <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1485,7 +1488,7 @@
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -1508,7 +1511,7 @@
       <c r="E5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1531,7 +1534,7 @@
       <c r="E6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1554,7 +1557,7 @@
       <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1577,7 +1580,7 @@
       <c r="E8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>29</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1600,7 +1603,7 @@
       <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -1623,7 +1626,7 @@
       <c r="E10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -1646,7 +1649,7 @@
       <c r="E11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -1669,7 +1672,7 @@
       <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -1686,13 +1689,13 @@
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>44</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -1715,7 +1718,7 @@
       <c r="E14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>47</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -1738,7 +1741,7 @@
       <c r="E15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>50</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -1761,7 +1764,7 @@
       <c r="E16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1784,7 +1787,7 @@
       <c r="E17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="6" t="s">
         <v>56</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -1807,7 +1810,7 @@
       <c r="E18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -1830,7 +1833,7 @@
       <c r="E19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -1853,7 +1856,7 @@
       <c r="E20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G20" s="1" t="s">

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13500"/>
+    <workbookView windowWidth="29100" windowHeight="13480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$G$20</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="65">
+  <si>
+    <t>ID</t>
+  </si>
   <si>
     <t>STATUS</t>
   </si>
@@ -77,9 +83,6 @@
     <t>20250318202971766250</t>
   </si>
   <si>
-    <t>https://gravastar-com.myshopify.com</t>
-  </si>
-  <si>
     <t>https://18c8df-2.myshopify.com</t>
   </si>
   <si>
@@ -159,9 +162,6 @@
   </si>
   <si>
     <t>20260211200680384083</t>
-  </si>
-  <si>
-    <t>https://prqjdj-v9.myshopify.com</t>
   </si>
   <si>
     <t>https://marketing-212684499424.myshopify.com</t>
@@ -840,12 +840,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1375,18 +1378,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="19.0673076923077" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="19.0673076923077" style="1" customWidth="1"/>
-    <col min="2" max="2" width="47.6153846153846" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.4615384615385" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.4615384615385" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.1538461538462" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="19.0673076923077" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.0673076923077" style="1"/>
+    <col min="2" max="2" width="19.0673076923077" style="1" customWidth="1"/>
+    <col min="3" max="3" width="47.6153846153846" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.4615384615385" style="1" customWidth="1"/>
+    <col min="5" max="5" width="38.4615384615385" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.1538461538462" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="19.0673076923077" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1405,365 +1409,394 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1">
-        <v>0</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1">
-        <v>0</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1">
-        <v>0</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="1">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1">
-        <v>0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="1">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="1">
-        <v>0</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="1">
-        <v>0</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="1">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="1">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="F20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" t="s">
-        <v>9</v>
+      <c r="G20" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C9" r:id="rId1" display="https://tcl-rayneo.myshopify.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -1418,7 +1418,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -1458,7 +1458,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
@@ -1478,7 +1478,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>17</v>
@@ -1498,7 +1498,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -1518,7 +1518,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>23</v>
@@ -1538,7 +1538,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>26</v>
@@ -1578,7 +1578,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1598,7 +1598,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>35</v>
@@ -1618,7 +1618,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>38</v>
@@ -1638,7 +1638,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>41</v>
@@ -1658,7 +1658,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>44</v>
@@ -1678,7 +1678,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>47</v>
@@ -1698,7 +1698,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>50</v>
@@ -1718,7 +1718,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>53</v>
@@ -1738,7 +1738,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>56</v>
@@ -1758,7 +1758,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>59</v>
@@ -1778,7 +1778,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>62</v>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -1457,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>12</v>
@@ -1526,7 +1526,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>21</v>
@@ -1595,7 +1595,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>30</v>
@@ -1618,7 +1618,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>33</v>
@@ -1710,7 +1710,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>45</v>
@@ -1733,7 +1733,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>48</v>
@@ -1756,7 +1756,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>51</v>
@@ -1848,7 +1848,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>63</v>

--- a/live_widget登陆店铺.xlsx
+++ b/live_widget登陆店铺.xlsx
@@ -1526,7 +1526,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>21</v>
@@ -1618,7 +1618,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>33</v>
